--- a/Data/EXCEL/Transfer/salemon/20240711/6671-salemon-20240711.xlsx
+++ b/Data/EXCEL/Transfer/salemon/20240711/6671-salemon-20240711.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlsx\20240711\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\GithubProjects\GoodinfoData2DB\Data\EXCEL\Transfer\salemon\20240711\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DC76ECBA-3EF4-4A39-9667-C919EE21C383}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5444811D-95DA-4E57-B2D1-2F91A0A6CBD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="290" windowWidth="18240" windowHeight="13390" xr2:uid="{AFFDE749-3F7E-4C4F-99C5-DB26190B6563}"/>
+    <workbookView xWindow="768" yWindow="684" windowWidth="20004" windowHeight="13956" xr2:uid="{7E6E01BB-AFFA-444C-8DC2-468F756DC7C7}"/>
   </bookViews>
   <sheets>
     <sheet name="6671-salemon-20240711" sheetId="2" r:id="rId1"/>
@@ -1261,18 +1261,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B2DE300-7F7E-49D1-A88D-B6AC21D24E59}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E86FECA-075E-4E09-9C64-188F5A7B0CBA}">
   <dimension ref="A1:Q146"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="17" width="5.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="17" width="5.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -1299,7 +1299,7 @@
       <c r="P1" s="19"/>
       <c r="Q1" s="20"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="16"/>
       <c r="B2" s="15" t="s">
         <v>4</v>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="16"/>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
@@ -1381,7 +1381,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -1420,7 +1420,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>45444</v>
       </c>
@@ -1473,7 +1473,7 @@
         <v>5.45</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="9">
         <v>45413</v>
       </c>
@@ -1526,7 +1526,7 @@
         <v>6.08</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>45383</v>
       </c>
@@ -1579,7 +1579,7 @@
         <v>7.22</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="9">
         <v>45352</v>
       </c>
@@ -1632,7 +1632,7 @@
         <v>9.3000000000000007</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>45323</v>
       </c>
@@ -1685,7 +1685,7 @@
         <v>26.6</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="9">
         <v>45292</v>
       </c>
@@ -1738,7 +1738,7 @@
         <v>121.3</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>45261</v>
       </c>
@@ -1791,7 +1791,7 @@
         <v>2.14</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="9">
         <v>45231</v>
       </c>
@@ -1844,7 +1844,7 @@
         <v>2.65</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>45200</v>
       </c>
@@ -1897,7 +1897,7 @@
         <v>2.42</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="9">
         <v>45170</v>
       </c>
@@ -1950,7 +1950,7 @@
         <v>2.41</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>45139</v>
       </c>
@@ -2003,7 +2003,7 @@
         <v>2.19</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="9">
         <v>45108</v>
       </c>
@@ -2056,7 +2056,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>45078</v>
       </c>
@@ -2109,7 +2109,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="9">
         <v>45047</v>
       </c>
@@ -2162,7 +2162,7 @@
         <v>-7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>45017</v>
       </c>
@@ -2215,7 +2215,7 @@
         <v>-2.59</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="9">
         <v>44986</v>
       </c>
@@ -2268,7 +2268,7 @@
         <v>-8.25</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>44958</v>
       </c>
@@ -2321,7 +2321,7 @@
         <v>-23</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="9">
         <v>44927</v>
       </c>
@@ -2374,7 +2374,7 @@
         <v>-51.2</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>44896</v>
       </c>
@@ -2427,7 +2427,7 @@
         <v>-9.82</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="9">
         <v>44866</v>
       </c>
@@ -2480,7 +2480,7 @@
         <v>-10.4</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>44835</v>
       </c>
@@ -2533,7 +2533,7 @@
         <v>-8.7899999999999991</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" s="9">
         <v>44805</v>
       </c>
@@ -2586,7 +2586,7 @@
         <v>-8.59</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>44774</v>
       </c>
@@ -2639,7 +2639,7 @@
         <v>-8.7799999999999994</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="9">
         <v>44743</v>
       </c>
@@ -2692,7 +2692,7 @@
         <v>-7.67</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>44713</v>
       </c>
@@ -2745,7 +2745,7 @@
         <v>-8.69</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="9">
         <v>44682</v>
       </c>
@@ -2798,7 +2798,7 @@
         <v>-6.93</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
         <v>44652</v>
       </c>
@@ -2851,7 +2851,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" s="9">
         <v>44621</v>
       </c>
@@ -2904,7 +2904,7 @@
         <v>-3.42</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>44593</v>
       </c>
@@ -2957,7 +2957,7 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" s="9">
         <v>44562</v>
       </c>
@@ -3010,7 +3010,7 @@
         <v>4.29</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>44531</v>
       </c>
@@ -3063,7 +3063,7 @@
         <v>8.01</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" s="9">
         <v>44501</v>
       </c>
@@ -3116,7 +3116,7 @@
         <v>8.89</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
         <v>44470</v>
       </c>
@@ -3169,7 +3169,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="9">
         <v>44440</v>
       </c>
@@ -3222,7 +3222,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
         <v>44409</v>
       </c>
@@ -3275,7 +3275,7 @@
         <v>13.1</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" s="9">
         <v>44378</v>
       </c>
@@ -3328,7 +3328,7 @@
         <v>14.1</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>44348</v>
       </c>
@@ -3381,7 +3381,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" s="9">
         <v>44317</v>
       </c>
@@ -3434,7 +3434,7 @@
         <v>16.399999999999999</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" s="5">
         <v>44287</v>
       </c>
@@ -3487,7 +3487,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" s="9">
         <v>44256</v>
       </c>
@@ -3540,7 +3540,7 @@
         <v>36.6</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" s="5">
         <v>44228</v>
       </c>
@@ -3593,7 +3593,7 @@
         <v>44.6</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" s="9">
         <v>44197</v>
       </c>
@@ -3646,7 +3646,7 @@
         <v>91.2</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" s="5">
         <v>44166</v>
       </c>
@@ -3699,7 +3699,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" s="9">
         <v>44136</v>
       </c>
@@ -3752,7 +3752,7 @@
         <v>0.71</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" s="5">
         <v>44105</v>
       </c>
@@ -3805,7 +3805,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" s="9">
         <v>44075</v>
       </c>
@@ -3858,7 +3858,7 @@
         <v>0.62</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" s="5">
         <v>44044</v>
       </c>
@@ -3911,7 +3911,7 @@
         <v>-1.01</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" s="9">
         <v>44013</v>
       </c>
@@ -3964,7 +3964,7 @@
         <v>-1.73</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" s="5">
         <v>43983</v>
       </c>
@@ -4017,7 +4017,7 @@
         <v>-3.23</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" s="9">
         <v>43952</v>
       </c>
@@ -4070,7 +4070,7 @@
         <v>-6.31</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" s="5">
         <v>43922</v>
       </c>
@@ -4123,7 +4123,7 @@
         <v>-10.3</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" s="9">
         <v>43891</v>
       </c>
@@ -4176,7 +4176,7 @@
         <v>-14.5</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" s="5">
         <v>43862</v>
       </c>
@@ -4229,7 +4229,7 @@
         <v>-29</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" s="9">
         <v>43831</v>
       </c>
@@ -4282,7 +4282,7 @@
         <v>-44.5</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" s="5">
         <v>43800</v>
       </c>
@@ -4335,7 +4335,7 @@
         <v>-0.69</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" s="9">
         <v>43770</v>
       </c>
@@ -4388,7 +4388,7 @@
         <v>-0.75</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" s="5">
         <v>43739</v>
       </c>
@@ -4441,7 +4441,7 @@
         <v>-1.18</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" s="9">
         <v>43709</v>
       </c>
@@ -4494,7 +4494,7 @@
         <v>-2.56</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" s="5">
         <v>43678</v>
       </c>
@@ -4547,7 +4547,7 @@
         <v>-1.89</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" s="9">
         <v>43647</v>
       </c>
@@ -4600,7 +4600,7 @@
         <v>-3.96</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" s="5">
         <v>43617</v>
       </c>
@@ -4653,7 +4653,7 @@
         <v>-6.73</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" s="9">
         <v>43586</v>
       </c>
@@ -4706,7 +4706,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" s="5">
         <v>43556</v>
       </c>
@@ -4759,7 +4759,7 @@
         <v>-7.04</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" s="9">
         <v>43525</v>
       </c>
@@ -4812,7 +4812,7 @@
         <v>-11.4</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" s="5">
         <v>43497</v>
       </c>
@@ -4865,7 +4865,7 @@
         <v>-11.9</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" s="9">
         <v>43466</v>
       </c>
@@ -4918,7 +4918,7 @@
         <v>-19.3</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" s="5">
         <v>43435</v>
       </c>
@@ -4971,7 +4971,7 @@
         <v>-6.34</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" s="9">
         <v>43405</v>
       </c>
@@ -5024,7 +5024,7 @@
         <v>-6.23</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" s="5">
         <v>43374</v>
       </c>
@@ -5077,367 +5077,367 @@
         <v>-6.68</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" s="5">
         <v>45444</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" s="9">
         <v>45413</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" s="5">
         <v>45383</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" s="9">
         <v>45352</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" s="5">
         <v>45323</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" s="9">
         <v>45292</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A81" s="5">
         <v>45261</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A82" s="9">
         <v>45231</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A83" s="5">
         <v>45200</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A84" s="9">
         <v>45170</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A85" s="5">
         <v>45139</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A86" s="9">
         <v>45108</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A87" s="5">
         <v>45078</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A88" s="9">
         <v>45047</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A89" s="5">
         <v>45017</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A90" s="9">
         <v>44986</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A91" s="5">
         <v>44958</v>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A92" s="9">
         <v>44927</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A94" s="5">
         <v>44896</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A95" s="9">
         <v>44866</v>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A96" s="5">
         <v>44835</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A97" s="9">
         <v>44805</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A98" s="5">
         <v>44774</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A99" s="9">
         <v>44743</v>
       </c>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A100" s="5">
         <v>44713</v>
       </c>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A101" s="9">
         <v>44682</v>
       </c>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A102" s="5">
         <v>44652</v>
       </c>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A103" s="9">
         <v>44621</v>
       </c>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A104" s="5">
         <v>44593</v>
       </c>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A105" s="9">
         <v>44562</v>
       </c>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A106" s="5">
         <v>44531</v>
       </c>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A107" s="9">
         <v>44501</v>
       </c>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A108" s="5">
         <v>44470</v>
       </c>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A109" s="9">
         <v>44440</v>
       </c>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A110" s="5">
         <v>44409</v>
       </c>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A111" s="9">
         <v>44378</v>
       </c>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A112" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A113" s="5">
         <v>44348</v>
       </c>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A114" s="9">
         <v>44317</v>
       </c>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A115" s="5">
         <v>44287</v>
       </c>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A116" s="9">
         <v>44256</v>
       </c>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A117" s="5">
         <v>44228</v>
       </c>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A118" s="9">
         <v>44197</v>
       </c>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A119" s="5">
         <v>44166</v>
       </c>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A120" s="9">
         <v>44136</v>
       </c>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A121" s="5">
         <v>44105</v>
       </c>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A122" s="9">
         <v>44075</v>
       </c>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A123" s="5">
         <v>44044</v>
       </c>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A124" s="9">
         <v>44013</v>
       </c>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A125" s="5">
         <v>43983</v>
       </c>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A126" s="9">
         <v>43952</v>
       </c>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A127" s="5">
         <v>43922</v>
       </c>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A128" s="9">
         <v>43891</v>
       </c>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A129" s="5">
         <v>43862</v>
       </c>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A130" s="9">
         <v>43831</v>
       </c>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A131" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A132" s="5">
         <v>43800</v>
       </c>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A133" s="9">
         <v>43770</v>
       </c>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A134" s="5">
         <v>43739</v>
       </c>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A135" s="9">
         <v>43709</v>
       </c>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A136" s="5">
         <v>43678</v>
       </c>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A137" s="9">
         <v>43647</v>
       </c>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A138" s="5">
         <v>43617</v>
       </c>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A139" s="9">
         <v>43586</v>
       </c>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A140" s="5">
         <v>43556</v>
       </c>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A141" s="9">
         <v>43525</v>
       </c>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A142" s="5">
         <v>43497</v>
       </c>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A143" s="9">
         <v>43466</v>
       </c>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A144" s="5">
         <v>43435</v>
       </c>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A145" s="9">
         <v>43405</v>
       </c>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A146" s="5">
         <v>43374</v>
       </c>
